--- a/Result/profitability/4916.xlsx
+++ b/Result/profitability/4916.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM68"/>
+  <dimension ref="A1:AM69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>6.18</v>
       </c>
       <c r="M2" t="n">
-        <v>1.6775</v>
+        <v>1.76375</v>
       </c>
       <c r="N2" t="n">
-        <v>18.40875</v>
+        <v>18.82125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>7.2</v>
       </c>
       <c r="M3" t="n">
-        <v>2.54375</v>
+        <v>2.58</v>
       </c>
       <c r="N3" t="n">
-        <v>18.14875</v>
+        <v>18.21375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>2.88</v>
       </c>
       <c r="M4" t="n">
-        <v>2.82</v>
+        <v>2.865</v>
       </c>
       <c r="N4" t="n">
-        <v>17.79625</v>
+        <v>17.70625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.75</v>
       </c>
       <c r="M5" t="n">
-        <v>2.83875</v>
+        <v>2.95375</v>
       </c>
       <c r="N5" t="n">
-        <v>16.9675</v>
+        <v>17.0475</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>3.09</v>
       </c>
       <c r="M6" t="n">
-        <v>3.22</v>
+        <v>3.2775</v>
       </c>
       <c r="N6" t="n">
-        <v>17.1675</v>
+        <v>17.2675</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>5.75</v>
       </c>
       <c r="M7" t="n">
-        <v>3.87625</v>
+        <v>3.9125</v>
       </c>
       <c r="N7" t="n">
-        <v>18.48125</v>
+        <v>18.74</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>2.71</v>
       </c>
       <c r="M8" t="n">
-        <v>4.13125</v>
+        <v>3.69</v>
       </c>
       <c r="N8" t="n">
-        <v>19.60125</v>
+        <v>19.6825</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9068,6 +9068,133 @@
       </c>
       <c r="AM68" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>4916</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1377</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1090</v>
+      </c>
+      <c r="E69" t="n">
+        <v>286</v>
+      </c>
+      <c r="F69" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="G69" t="n">
+        <v>149</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>10.82%</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>149</v>
+      </c>
+      <c r="K69" t="n">
+        <v>119</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="N69" t="n">
+        <v>19.8925</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
+      </c>
+      <c r="V69" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W69" t="n">
+        <v>-3.53</v>
+      </c>
+      <c r="X69" t="n">
+        <v>-0.7861915367483296</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0.6500000000000021</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0.03225806451612923</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0.9199999999999999</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>0.6400000000000006</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0.03174603174603186</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK69" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
